--- a/2022 data/excel_outputs/173_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/173_boothwise_data.xlsx
@@ -14,9 +14,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="118">
   <si>
     <t>AC 173 Booth-wise Data</t>
+  </si>
+  <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
   </si>
   <si>
     <t>BOOTH ID</t>
@@ -25,1291 +103,196 @@
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>#### #### ######### ##### ##### ##### ###### ### #### ##0.1</t>
+    <t>NAN</t>
   </si>
   <si>
-    <t>#### #### ######### ##### ##### ##### ###### ### #### ##0.2</t>
+    <t>SHRAKL|PTHABHJKL|AIBHT AIAIBHDYACH AIBHT|THABHDYASHRCH|S|THABHBBH AIBHTBBH|KL|PK|PTHABHJDYAD DYACHJBH|THABHBBHSHRATHABHAIBHT THATHABHKL|AIKL|SHR JBH|THABHKL|PCH4</t>
   </si>
   <si>
-    <t>#### #### ######### ##### ##### ##### ###### ### #### ##0.3</t>
+    <t>NAN ROOM NO. 368</t>
   </si>
   <si>
-    <t>### #0##### ###### ###### #### #### ####### #### ##0.1</t>
+    <t>NAN ROOM ROOM NO. 369</t>
   </si>
   <si>
-    <t>### #0##### ###### ###### #### #### ####### #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM NO. 370</t>
   </si>
   <si>
-    <t>### #0##### ###### ###### #### #### ####### #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM NO. 371</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM NO. 372</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.7</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.8</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.9</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
   </si>
   <si>
-    <t>####### ######### ##### ##### ###### ### #### ##0.10</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
   </si>
   <si>
-    <t>##0##0######### #### ### #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
   </si>
   <si>
-    <t>##0##0######### #### ### #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
   </si>
   <si>
-    <t>##0##0######### #### ### #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
   </si>
   <si>
-    <t>##0##0######### #### ### #### ##0.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
   </si>
   <si>
-    <t>#### ###### ###### ##### ### ######### #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
   </si>
   <si>
-    <t>#### ###### ###### ##### ### ######### #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
   </si>
   <si>
-    <t>#### ###### ###### ##### ### ######### #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
   </si>
   <si>
-    <t>#### ###### ###### ##### ### ######### #### ##0.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
   </si>
   <si>
-    <t>#### ###### ###### ##### ### ######### #### ##0.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
   </si>
   <si>
-    <t>####### ##### ###### ##### ##### ######## ##### ###### ######### #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
   </si>
   <si>
-    <t>####### ##### ###### ##### ##### ######## ##### ###### ######### #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
   </si>
   <si>
-    <t>####### ##### ###### ##### ##### ######## ##### ###### ######### #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
   </si>
   <si>
-    <t>######## ### ###### ###### ###### ### #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
   </si>
   <si>
-    <t>######## ### ###### ###### ###### ### #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
   </si>
   <si>
-    <t>######## ### ###### ###### ###### ### #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
   </si>
   <si>
-    <t>######## ### ###### ###### ###### ### #### ##0.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
   </si>
   <si>
-    <t>######## ### ###### ###### ###### ### #### ##0.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
   </si>
   <si>
-    <t>######## ### ###### ###### ###### ### #### ##0.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
   </si>
   <si>
-    <t>######## ### ###### ###### ###### ### #### ##0.7</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
   </si>
   <si>
-    <t>###### #### ##### ##### ##### ###### ##### ###### ### #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
   </si>
   <si>
-    <t>###### #### ##### ##### ##### ###### ##### ###### ### #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
   </si>
   <si>
-    <t>###### #### ##### ##### ##### ###### ##### ###### ### #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
   </si>
   <si>
-    <t>###### #### ##### ##### ##### ###### ##### ###### ### #### ##0.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
   </si>
   <si>
-    <t>###### #### ##### ##### ##### ###### ##### ###### ### #### ##0.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.6</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.7</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.8</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.9</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.10</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.11</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.12</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.13</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
   </si>
   <si>
-    <t>###### ###### #0 ##### #########.1 #### ##0.14</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
   </si>
   <si>
-    <t>##### ##0##0##### #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
   </si>
   <si>
-    <t>##### ##0##0##### #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
   </si>
   <si>
-    <t>##### ##0##0##### #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
   </si>
   <si>
-    <t>##### ##0##0##### #### ##0.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
   </si>
   <si>
-    <t>####0######## ##### #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
   </si>
   <si>
-    <t>####0######## ##### #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
   </si>
   <si>
-    <t>##### ###### ######## e######## #### ##0.1</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
   </si>
   <si>
-    <t>##### ###### ######## e######## #### ##0.2</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
   </si>
   <si>
-    <t>##### ###### ######## e######## #### ##0.3</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
   </si>
   <si>
-    <t>##### ###### ######## e######## #### ##0.4</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.5</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.6</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.7</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.8</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.9</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.10</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.11</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.12</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.13</t>
-  </si>
-  <si>
-    <t>##### ###### ######## e######## #### ##0.14</t>
-  </si>
-  <si>
-    <t>#### ###### ######### ####### ##.21 ###### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ###### ######### ####### ##.21 ###### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ###### ######### ####### ##.21 ###### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ###### ######### ####### ##.21 ###### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>###### ###### ####0####0#### ##025 ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ###### ####0####0#### ##025 ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>###### ###### ####0####0#### ##025 ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##0 19 ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##0 19 ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##0 19 ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##0 19 ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##0 19 ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### ###### ##### ##0 19 ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>######## ### ##### ###### ##### ##.17 ##### ##### ####### ### #### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ### ##### ###### ##### ##.17 ##### ##### ####### ### #### #### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ### ##### ###### ##### ##.17 ##### ##### ####### ### #### #### ##0.3</t>
-  </si>
-  <si>
-    <t>######## ### ##### ###### ##### ##.17 ##### ##### ####### ### #### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.8</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.9</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.10</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####0######### ##### ##.14 ####### ### #### ##0.11</t>
-  </si>
-  <si>
-    <t>###0###### #0##### ##0 11 ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###0###### #0##### ##0 11 ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>###0###### #0##### ##0 11 ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>###0###### #0##### ##0 11 ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>###0###### #0##### ##0 11 ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### ####### ###### ###### ###### ######### ##### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ####### ###### ###### ###### ######### ##### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ####### ###### ###### ###### ######### ##### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ####### ###### ###### ###### ######### ##### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### ####### ###### ###### ###### ######### ##### #### ##0.5</t>
-  </si>
-  <si>
-    <t>######## ######### ##### ##### ### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ######### ##### ##### ### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0##0 ######## ###### ##### ######## #### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##0##0 ######## ###### ##### ######## #### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0##0##0###### ##### ##### ##### ### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##0##0##0###### ##### ##### ##### ### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0##0##0###### ##### ##### ##### ### ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##0##0##0###### ##### ##### ##### ### ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>####### ###### ###### ##### 51 #### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####### ###### ###### ##### 51 #### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### ###### ###### ##### 51 #### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### ###### ###### ##### 51 #### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>####### ###### ###### ##### 51 #### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ### #### ###### ##### ######### ### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ### #### ###### ##### ######### ### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ### #### ###### ##### ######### ### ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ### #### ###### ##### ######### ### ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ### #### ###### ##### ######### ### ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>######## ###### ##0 9 ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ###### ##0 9 ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ###### ##0 9 ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>######## ###### ##0 9 ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>######## ###### ##0 9 ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>######## ###### ##0 9 ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>######## ###### ##0 9 ####### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>######## ###### ##0 9 ####### ### #### ##0.8</t>
-  </si>
-  <si>
-    <t>######## ###### ##0 9 ####### ### #### ##0.9</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ##.8 ########## ##### ####### ## #### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ##.8 ########## ##### ####### ## #### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ##.8 ########## ##### ####### ## #### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ####### ### ######## ##### #### ### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ####### ### ######## ##### #### ### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ####### ### ######## ##### #### ### ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ####### ### ######## ##### #### ### ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### ###### ###### #0##### ##### ### ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ###### ###### #0##### ##### ### ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### ###### #0 ##### #### ##### ###### #### ### ##.##### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####### ###### #0 ##### #### ##### ###### #### ### ##.##### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### ###### #0 ##### #### ##### ###### #### ### ##.##### ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### ###### #0 ##### #### ##### ###### #### ### ##.##### ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>####### ###### #0 ##### #### ##### ###### #### ### ##.##### ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>####### ###### #0 ##### #### ##### ###### #### ### ##.##### ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>####### ###### #0 ##### #### ##### ###### #### ### ##.##### ####### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>#### ##### ##0 15 ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ##### ##0 15 ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ##### ##0 15 ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ##### ##0 15 ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### ##### ##0 15 ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### ##### ##0 15 ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>#### ##### ##0 15 ####### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ## ##### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ## ##### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ## ##### ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ## ##### ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ## ##### ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ## ##### ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ## ##### ####### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### ## ##### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### ## ##### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### ## ##### ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### ## ##### ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### ## ##### ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### ## ##### ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### ## ##### ####### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>###### ########### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ########### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####0######## ####### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####0######## ####### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####0######## ####### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####0######## ####### #### ##0.4</t>
-  </si>
-  <si>
-    <t>####0######## ####### #### ##0.5</t>
-  </si>
-  <si>
-    <t>####### ###### ## ##### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####### ###### ## ##### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### ###### ## ##### ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### ###### ## ##### ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>####### ###### ## ##### ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>####### ###### ## ##### ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>####### #### ###### # ##### ###### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####### #### ###### # ##### ###### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### #### ###### # ##### ###### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### #### ###### # ##### ###### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>####### #### ###### # ##### ###### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>####### #### ###### # ##### ###### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ######## ###### ##.23 ########## #### ##0.1</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ######## ###### ##.23 ########## #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ######## ###### ##.23 ########## #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### ###### ##### ######## ###### ##.23 ########## #### ##0.4</t>
-  </si>
-  <si>
-    <t>########### ##### # ##### ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>########### ##### # ##### ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>########### ##### # ##### ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>########### ##### # ##### ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>########### ##### # ##### ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>########### ##### # ##### ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>########### ##### # ##### ####### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>########### ##### # ##### ####### ### #### ##0.8</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### e##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### e##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### e##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>### ###### ###### ##### e##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>############# ###### ##### ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>############# ###### ##### ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>######### ####### ######### ###### ### ####### ##### #### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######### ####### ######### ###### ### ####### ##### #### #### ##0.2</t>
-  </si>
-  <si>
-    <t>########### ##### ##### e ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>########### ##### ##### e ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>########### ##### ##### e ###### #### ##0.3</t>
-  </si>
-  <si>
-    <t>########### ##### ##### e ###### #### ##0.4</t>
-  </si>
-  <si>
-    <t>########### ##### ##### e ###### #### ##0.5</t>
-  </si>
-  <si>
-    <t>##### ########### ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##### ########### ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##### ########### ###### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##### ########### ###### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.8</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.9</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ### #### ##0.10</t>
-  </si>
-  <si>
-    <t>#### ####### ### ######## ##### #### ### ###### ##### ## ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ####### ### ######## ##### #### ### ###### ##### ## ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##### ######### ##### #### ### ###### ##### ## ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##### ######### ##### #### ### ###### ##### ## ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##### ######### ##### #### ### ###### ##### ## ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##### ######### ##### #### ### ###### ##### ## ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##### ######### ##### #### ### ###### ##### ## ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ##### ##### ###### ###### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ##### ##### ###### ###### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ##### ##### ###### ###### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ##### ##### ###### ###### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ##### ##### ###### ###### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ##### ##### ###### ###### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ##### ##### ###### ###### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ##### ##### ###### ###### ### #### ##0.8</t>
-  </si>
-  <si>
-    <t>#### ### ###### ###### ##### ##### ###### ###### ### #### ##0.9</t>
-  </si>
-  <si>
-    <t>######### ###### #0##### ######### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######### ###### #0##### ######### #### ##0.2</t>
-  </si>
-  <si>
-    <t>######### ###### #0##### ######### #### ##0.3</t>
-  </si>
-  <si>
-    <t>###### ##0 ##### ###### ##0 5 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ##0 ##### ###### ##0 5 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>###### ##0 ##### ###### ##0 5 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>###### ##0 ##### ###### ##0 5 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>###### ##0 ##### ###### ##0 5 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>###### ##0 ##### ###### ##0 5 ##### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>###### ##0 ##### ###### ##0 5 ##### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>###### ##0 ##### ###### ##0 5 ##### ### #### ##0.8</t>
-  </si>
-  <si>
-    <t>###### ##0###### #0##### ##0 5 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ##0###### #0##### ##0 5 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>###### ##0###### #0##### ##0 5 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>###### ##0###### #0##### ##0 5 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>###### ##0###### #0##### ##0 5 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>####### ##0 ##### ##0 1 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####### ##0 ##### ##0 1 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### ##0 ##### ##0 1 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### ##0 ##### ##0 1 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0 3 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0 3 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0 3 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0 3 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0 3 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0 3 ##### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0 3 ##### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0 3 ##### ### #### ##0.8</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0 3 ##### ### #### ##0.9</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##0 6 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##0 6 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##0 6 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##0 6 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##0 6 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##0 6 ##### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>##0##0##0##### ##0 6 ##### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>#### ###### ##### #### ### ########## ###### ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ###### ##### #### ### ########## ###### ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ###### ##### #### ### ########## ###### ###### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ###### ##### #### ### ########## ###### ###### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### ###### ##### #### ### ########## ###### ###### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### ###### ##### #### ### ########## ###### ###### #### ##0.6</t>
-  </si>
-  <si>
-    <t>##0######### ###### ###### ##### ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##0######### ###### ###### ##### ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##0######### ###### ###### ##### ###### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##0######### ###### ###### ##### ###### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##0######### ###### ###### ##### ###### #### ##0.5</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ##### ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ##### ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ##### ###### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ##### ###### #### ##0.4</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ##### ###### #### ##0.5</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ##### ###### #### ##0.6</t>
-  </si>
-  <si>
-    <t>#### ##### ;###ddhe #### ### ###dh1</t>
-  </si>
-  <si>
-    <t>#### ##### ;###ddhe #### ### ###dh2</t>
-  </si>
-  <si>
-    <t>#### ##### ;###ddhe #### ### ###dh3</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ##### ### #####e #### ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ##### ### #####e #### ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>###### ######## ###### ##### ### #####e #### ######## #### ##0.3</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ###### ##### #### #### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ###### ##### #### #### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ###### ##### #### #### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ##### ####### ##### ##### ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ##### ####### ##### ##### ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ##### ####### ##### ##### ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ##### ####### ##### ##### ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### ##### ####### ##### ##### ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### ### ##### ######## ###### ##### ##### #### ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### ### ##### ######## ###### ##### ##### #### ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ### ##### ######## ###### ##### ##### #### ######## #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### ### ##### ######## ###### ##### ##### #### ######## #### ##0.4</t>
-  </si>
-  <si>
-    <t>####### ######## ######## ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####### ######## ######## ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### ######## ######## ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### ######## ######## ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>####### ######## ######## ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ##### ##### ####### ###### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ##### ##### ####### ###### #### ##0.2</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ##### ##### ####### ###### #### ##0.3</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ##### ##### ####### ###### #### ##0.4</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ##### ##### ####### ###### #### ##0.5</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ##### ##### ####### ###### #### ##0.6</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ##### ##### ####### ###### #### ##0.7</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ##### ##### ####### ###### #### ##0.8</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #### ##### ##### ####### ###### #### ##0.9</t>
-  </si>
-  <si>
-    <t>##### ####### ####### ;###ddh ###### ### ###### ## ### ### ##0.1</t>
-  </si>
-  <si>
-    <t>##### ########## ##### ####### ### ###### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##### ########## ##### ####### ### ###### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##### ########## ##### ####### ### ###### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##### ########## ##### ####### ### ###### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>### ######### ##### #### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>### ######### ##### #### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>### ######### ##### #### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ######## ##### ###### ##### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ######## ##### ###### ##### #### ##0.2</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ######## ##### ###### ##### #### ##0.3</t>
-  </si>
-  <si>
-    <t>####### #### ##### ##### ######## ##### ###### ##### #### ##0.4</t>
-  </si>
-  <si>
-    <t>######## ### ############# #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ### ############# #### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ## ##### ########### ###### #### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ## ##### ########### ###### #### #### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ## ##### ########### ###### #### #### ##0.3</t>
-  </si>
-  <si>
-    <t>######## ## ##### ########### ###### #### #### ##0.4</t>
-  </si>
-  <si>
-    <t>######## ## ##### ########### ###### #### #### ##0.5</t>
-  </si>
-  <si>
-    <t>######## ## ##### ########### ###### #### #### ##0.6</t>
-  </si>
-  <si>
-    <t>######## ######## ####.2 #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ######## ####.2 #### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ######## ####.2 #### ##0.3</t>
-  </si>
-  <si>
-    <t>######### ### ### ######### #### ### ####### ##### ## ####### #### ########## #### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######### ### ### ######### #### ### ####### ##### ## ####### #### ########## #### #### ##0.2</t>
-  </si>
-  <si>
-    <t>######### ### ### ######### #### ### ####### ##### ## ####### #### ########## #### #### ##0.3</t>
-  </si>
-  <si>
-    <t>######### ### ### ######### #### ### ####### ##### ## ####### #### ########## #### #### ##0.4</t>
-  </si>
-  <si>
-    <t>######### ### ### ######### #### ### ####### ##### ## ####### #### ########## #### #### ##0.5</t>
-  </si>
-  <si>
-    <t>### ##0##0##### #### #### ##0.1</t>
-  </si>
-  <si>
-    <t>### ##0##0##### #### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ##### #### ##### ### #### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ##### #### ##### ### #### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ##### #### ##### ### #### #### ##0.3</t>
-  </si>
-  <si>
-    <t>### ## ## ######## ##### ##### #### ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>### ## ## ######## ##### ##### #### ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>### ## ## ######## ##### ##### #### ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>### ## ## ######## ##### ##### #### ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>### ## ## ######## ##### ##### #### ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>### ## ## ######## ##### ##### #### ##### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>### ## ## ######## ##### ##### #### ##### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>### ## ## ######## ##### ##### #### ##### ### #### ##0.8</t>
-  </si>
-  <si>
-    <t>####0######## ##### ##### ##### ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####0######## ##### ##### ##### ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### ####0######## ##### ##### ##### ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>####0######## ### #### ##### ######## #### ##0.1</t>
-  </si>
-  <si>
-    <t>####0######## ### #### ##### ######## #### ##0.2</t>
-  </si>
-  <si>
-    <t>####0######## ### #### ##### ######## #### ##0.3</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ####.5 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ####.5 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ####.5 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ####.5 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ####.5 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### #### ###### ##### ####.1 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>#### #### ###### ##### ####.1 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>#### #### ###### ##### ####.1 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>#### #### ###### ##### ####.1 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>#### #### ###### ##### ####.1 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>#### #### ###### ##### ####.1 ##### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>#### #### ###### ##### ####.1 ##### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>### ####### ##### ###### ##### #### ####.1 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>### ####### ##### ###### ##### #### ####.1 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>### ####### ##### ###### ##### #### ####.1 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>### ####### ##### ###### ##### #### ####.1 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>### ####### ##### ###### ##### #### ####.1 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>### ####### ##### ###### ##### #### ####.1 ##### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ########.4 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ########.4 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ########.4 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ########.4 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ########.4 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ########.4 ##### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ########.4 ##### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>##### ### ###### ##### ##### ####.3 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##### ### ###### ##### ##### ####.3 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##### ### ###### ##### ##### ####.3 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##### ### ###### ##### ##### ####.3 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##### ### ###### ##### ##### ####.3 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>##### ### ###### ##### ##### ####.3 ##### ### #### ##0.6</t>
-  </si>
-  <si>
-    <t>##### ### ###### ##### ##### ####.3 ##### ### #### ##0.7</t>
-  </si>
-  <si>
-    <t>##### ### ###### ##### ##### ####.3 ##### ### #### ##0.8</t>
-  </si>
-  <si>
-    <t>##### ###### #### ######### ##### ####### ####.2 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>##### ###### #### ######### ##### ####### ####.2 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>##### ###### #### ######### ##### ####### ####.2 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>##### ###### #### ######### ##### ####### ####.2 ##### ### #### ##0.4</t>
-  </si>
-  <si>
-    <t>##### ###### #### ######### ##### ####### ####.2 ##### ### #### ##0.5</t>
-  </si>
-  <si>
-    <t>######## ###### ######.4 ##### ### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ###### ######.4 ##### ### #### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ###### ######.4 ##### ### #### ##0.3</t>
-  </si>
-  <si>
-    <t>######## ###### ######.4 ##### ### #### ##0.4</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -1391,8 +374,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1408,7 +399,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1416,12 +407,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1720,91 +729,169 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>433</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>434</v>
+        <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>435</v>
+        <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>436</v>
+        <v>97</v>
       </c>
       <c r="H2" t="s">
-        <v>437</v>
+        <v>98</v>
       </c>
       <c r="I2" t="s">
-        <v>438</v>
+        <v>99</v>
       </c>
       <c r="J2" t="s">
-        <v>439</v>
+        <v>100</v>
       </c>
       <c r="K2" t="s">
-        <v>440</v>
+        <v>101</v>
       </c>
       <c r="L2" t="s">
-        <v>441</v>
+        <v>102</v>
       </c>
       <c r="M2" t="s">
-        <v>442</v>
+        <v>103</v>
       </c>
       <c r="N2" t="s">
-        <v>443</v>
+        <v>104</v>
       </c>
       <c r="O2" t="s">
-        <v>444</v>
+        <v>105</v>
       </c>
       <c r="P2" t="s">
-        <v>445</v>
+        <v>106</v>
       </c>
       <c r="Q2" t="s">
-        <v>446</v>
+        <v>107</v>
       </c>
       <c r="R2" t="s">
-        <v>447</v>
+        <v>108</v>
       </c>
       <c r="S2" t="s">
-        <v>448</v>
+        <v>109</v>
       </c>
       <c r="T2" t="s">
-        <v>449</v>
+        <v>110</v>
       </c>
       <c r="U2" t="s">
-        <v>450</v>
+        <v>111</v>
       </c>
       <c r="V2" t="s">
-        <v>451</v>
+        <v>112</v>
       </c>
       <c r="W2" t="s">
-        <v>452</v>
+        <v>113</v>
       </c>
       <c r="X2" t="s">
-        <v>453</v>
+        <v>114</v>
       </c>
       <c r="Y2" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="Z2" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
       <c r="AA2" t="s">
-        <v>456</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -1812,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>631</v>
@@ -1895,7 +982,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>1213</v>
@@ -1978,7 +1065,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>1220</v>
@@ -2061,7 +1148,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>943</v>
@@ -2144,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>935</v>
@@ -2227,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>903</v>
@@ -2310,7 +1397,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>988</v>
@@ -2393,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>1047</v>
@@ -2476,7 +1563,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>887</v>
@@ -2559,7 +1646,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C12">
         <v>1206</v>
@@ -2642,7 +1729,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C13">
         <v>1107</v>
@@ -2725,7 +1812,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>1022</v>
@@ -2808,7 +1895,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>1093</v>
@@ -2891,7 +1978,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C16">
         <v>1188</v>
@@ -2974,7 +2061,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>1148</v>
@@ -3057,7 +2144,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C18">
         <v>1166</v>
@@ -3140,7 +2227,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C19">
         <v>1081</v>
@@ -3223,7 +2310,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C20">
         <v>1105</v>
@@ -3306,7 +2393,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>965</v>
@@ -3389,7 +2476,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C22">
         <v>1095</v>
@@ -3472,7 +2559,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C23">
         <v>1117</v>
@@ -3555,7 +2642,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>1163</v>
@@ -3638,7 +2725,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C25">
         <v>1086</v>
@@ -3721,7 +2808,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C26">
         <v>1161</v>
@@ -3804,7 +2891,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>1254</v>
@@ -3887,7 +2974,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C28">
         <v>871</v>
@@ -4053,7 +3140,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30">
         <v>911</v>
@@ -4136,7 +3223,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C31">
         <v>1122</v>
@@ -4219,7 +3306,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C32">
         <v>1098</v>
@@ -4302,7 +3389,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C33">
         <v>1137</v>
@@ -4385,7 +3472,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C34">
         <v>1144</v>
@@ -4468,7 +3555,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C35">
         <v>1123</v>
@@ -4551,7 +3638,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C36">
         <v>1126</v>
@@ -4634,7 +3721,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C37">
         <v>1154</v>
@@ -4717,7 +3804,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C38">
         <v>1112</v>
@@ -4800,7 +3887,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C39">
         <v>1014</v>
@@ -4883,7 +3970,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C40">
         <v>1117</v>
@@ -4966,7 +4053,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C41">
         <v>1160</v>
@@ -5049,7 +4136,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C42">
         <v>1148</v>
@@ -5132,7 +4219,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="C43">
         <v>1123</v>
@@ -5215,7 +4302,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C44">
         <v>1090</v>
@@ -5298,7 +4385,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C45">
         <v>1142</v>
@@ -5381,7 +4468,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C46">
         <v>1191</v>
@@ -5464,7 +4551,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C47">
         <v>1079</v>
@@ -5547,7 +4634,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C48">
         <v>1242</v>
@@ -5630,7 +4717,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C49">
         <v>1223</v>
@@ -5713,7 +4800,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C50">
         <v>1137</v>
@@ -5796,7 +4883,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C51">
         <v>1165</v>
@@ -5879,7 +4966,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C52">
         <v>1135</v>
@@ -5962,7 +5049,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C53">
         <v>1065</v>
@@ -6045,7 +5132,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C54">
         <v>1093</v>
@@ -6128,7 +5215,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C55">
         <v>1118</v>
@@ -6211,7 +5298,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C56">
         <v>1083</v>
@@ -6294,7 +5381,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C57">
         <v>976</v>
@@ -6377,7 +5464,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C58">
         <v>1146</v>
@@ -6460,7 +5547,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C59">
         <v>1001</v>
@@ -6543,7 +5630,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C60">
         <v>909</v>
@@ -6626,7 +5713,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C61">
         <v>722</v>
@@ -6709,7 +5796,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C62">
         <v>698</v>
@@ -6792,7 +5879,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C63">
         <v>1027</v>
@@ -6875,7 +5962,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C64">
         <v>1161</v>
@@ -6958,7 +6045,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="C65">
         <v>1134</v>
@@ -7041,7 +6128,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="C66">
         <v>1229</v>
@@ -7124,7 +6211,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="C67">
         <v>1218</v>
@@ -7207,7 +6294,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C68">
         <v>1130</v>
@@ -7290,7 +6377,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="C69">
         <v>1178</v>
@@ -7373,7 +6460,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="C70">
         <v>1035</v>
@@ -7456,7 +6543,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="C71">
         <v>936</v>
@@ -7539,7 +6626,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C72">
         <v>1103</v>
@@ -7622,7 +6709,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="C73">
         <v>1094</v>
@@ -7705,7 +6792,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="C74">
         <v>1111</v>
@@ -7788,7 +6875,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="C75">
         <v>1071</v>
@@ -7871,7 +6958,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="C76">
         <v>941</v>
@@ -7954,7 +7041,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="C77">
         <v>825</v>
@@ -8037,7 +7124,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C78">
         <v>842</v>
@@ -8120,7 +7207,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C79">
         <v>982</v>
@@ -8203,7 +7290,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C80">
         <v>919</v>
@@ -8286,7 +7373,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="C81">
         <v>1138</v>
@@ -8369,7 +7456,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="C82">
         <v>1145</v>
@@ -8452,7 +7539,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="C83">
         <v>1078</v>
@@ -8535,7 +7622,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C84">
         <v>1101</v>
@@ -8618,7 +7705,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C85">
         <v>1016</v>
@@ -8701,7 +7788,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="C86">
         <v>1114</v>
@@ -8784,7 +7871,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="C87">
         <v>1010</v>
@@ -8867,7 +7954,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="C88">
         <v>1079</v>
@@ -8950,7 +8037,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="C89">
         <v>853</v>
@@ -9033,7 +8120,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="C90">
         <v>1011</v>
@@ -9116,7 +8203,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="C91">
         <v>1029</v>
@@ -9199,7 +8286,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="C92">
         <v>1024</v>
@@ -9282,7 +8369,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="C93">
         <v>959</v>
@@ -9365,7 +8452,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="C94">
         <v>1141</v>
@@ -9448,7 +8535,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C95">
         <v>1134</v>
@@ -9531,7 +8618,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="C96">
         <v>1055</v>
@@ -9614,7 +8701,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="C97">
         <v>1124</v>
@@ -9697,7 +8784,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="C98">
         <v>1137</v>
@@ -9780,7 +8867,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="C99">
         <v>1125</v>
@@ -9863,7 +8950,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="C100">
         <v>1170</v>
@@ -9946,7 +9033,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="C101">
         <v>1155</v>
@@ -10029,7 +9116,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="C102">
         <v>1159</v>
@@ -10112,7 +9199,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="C103">
         <v>1137</v>
@@ -10195,7 +9282,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="C104">
         <v>1096</v>
@@ -10278,7 +9365,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="C105">
         <v>1040</v>
@@ -10361,7 +9448,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="C106">
         <v>1039</v>
@@ -10444,7 +9531,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="C107">
         <v>1210</v>
@@ -10527,7 +9614,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="C108">
         <v>1132</v>
@@ -10610,7 +9697,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="C109">
         <v>1112</v>
@@ -10693,7 +9780,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="C110">
         <v>1146</v>
@@ -10776,7 +9863,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="C111">
         <v>1208</v>
@@ -10859,7 +9946,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="C112">
         <v>1097</v>
@@ -10942,7 +10029,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="C113">
         <v>1178</v>
@@ -11025,7 +10112,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>29</v>
       </c>
       <c r="C114">
         <v>1159</v>
@@ -11108,7 +10195,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="C115">
         <v>1119</v>
@@ -11191,7 +10278,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="C116">
         <v>973</v>
@@ -11274,7 +10361,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="C117">
         <v>1081</v>
@@ -11357,7 +10444,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="C118">
         <v>1137</v>
@@ -11440,7 +10527,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="C119">
         <v>954</v>
@@ -11523,7 +10610,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="C120">
         <v>963</v>
@@ -11606,7 +10693,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>29</v>
       </c>
       <c r="C121">
         <v>1196</v>
@@ -11689,7 +10776,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="C122">
         <v>1180</v>
@@ -11772,7 +10859,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="C123">
         <v>1106</v>
@@ -11855,7 +10942,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="C124">
         <v>1172</v>
@@ -11938,7 +11025,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="C125">
         <v>1155</v>
@@ -12021,7 +11108,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="C126">
         <v>1029</v>
@@ -12104,7 +11191,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="C127">
         <v>1090</v>
@@ -12187,7 +11274,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="C128">
         <v>1151</v>
@@ -12270,7 +11357,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="C129">
         <v>1045</v>
@@ -12353,7 +11440,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="C130">
         <v>1019</v>
@@ -12436,7 +11523,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="C131">
         <v>1051</v>
@@ -12519,7 +11606,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="C132">
         <v>1028</v>
@@ -12602,7 +11689,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="C133">
         <v>1024</v>
@@ -12685,7 +11772,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="C134">
         <v>1112</v>
@@ -12768,7 +11855,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="C135">
         <v>1094</v>
@@ -12851,7 +11938,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="C136">
         <v>1138</v>
@@ -12934,7 +12021,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>29</v>
       </c>
       <c r="C137">
         <v>1071</v>
@@ -13017,7 +12104,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="C138">
         <v>1098</v>
@@ -13100,7 +12187,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="C139">
         <v>1068</v>
@@ -13183,7 +12270,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="C140">
         <v>1124</v>
@@ -13266,7 +12353,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>29</v>
       </c>
       <c r="C141">
         <v>887</v>
@@ -13349,7 +12436,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="C142">
         <v>982</v>
@@ -13432,7 +12519,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="C143">
         <v>963</v>
@@ -13515,7 +12602,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="C144">
         <v>1129</v>
@@ -13598,7 +12685,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="C145">
         <v>1075</v>
@@ -13681,7 +12768,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="C146">
         <v>1080</v>
@@ -13764,7 +12851,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>29</v>
       </c>
       <c r="C147">
         <v>1113</v>
@@ -13847,7 +12934,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="C148">
         <v>1117</v>
@@ -13930,7 +13017,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="C149">
         <v>1127</v>
@@ -14013,7 +13100,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="C150">
         <v>1150</v>
@@ -14096,7 +13183,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>29</v>
       </c>
       <c r="C151">
         <v>1026</v>
@@ -14179,7 +13266,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="C152">
         <v>1128</v>
@@ -14262,7 +13349,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="C153">
         <v>974</v>
@@ -14345,7 +13432,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="C154">
         <v>1148</v>
@@ -14428,7 +13515,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c r="C155">
         <v>1064</v>
@@ -14511,7 +13598,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="C156">
         <v>1078</v>
@@ -14594,7 +13681,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="C157">
         <v>996</v>
@@ -14677,7 +13764,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>29</v>
       </c>
       <c r="C158">
         <v>979</v>
@@ -14760,7 +13847,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
       <c r="C159">
         <v>1149</v>
@@ -14843,7 +13930,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="C160">
         <v>1114</v>
@@ -14926,7 +14013,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="C161">
         <v>1099</v>
@@ -15009,7 +14096,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>29</v>
       </c>
       <c r="C162">
         <v>1123</v>
@@ -15092,7 +14179,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>29</v>
       </c>
       <c r="C163">
         <v>1065</v>
@@ -15175,7 +14262,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>29</v>
       </c>
       <c r="C164">
         <v>1045</v>
@@ -15258,7 +14345,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="C165">
         <v>1070</v>
@@ -15341,7 +14428,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="C166">
         <v>1047</v>
@@ -15424,7 +14511,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>29</v>
       </c>
       <c r="C167">
         <v>1072</v>
@@ -15507,7 +14594,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="C168">
         <v>1116</v>
@@ -15590,7 +14677,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="C169">
         <v>1035</v>
@@ -15673,7 +14760,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c r="C170">
         <v>929</v>
@@ -15756,7 +14843,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="C171">
         <v>985</v>
@@ -15839,7 +14926,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>29</v>
       </c>
       <c r="C172">
         <v>1063</v>
@@ -15922,7 +15009,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>29</v>
       </c>
       <c r="C173">
         <v>994</v>
@@ -16005,7 +15092,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>29</v>
       </c>
       <c r="C174">
         <v>1094</v>
@@ -16088,7 +15175,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="C175">
         <v>994</v>
@@ -16171,7 +15258,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>29</v>
       </c>
       <c r="C176">
         <v>881</v>
@@ -16254,7 +15341,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="C177">
         <v>1157</v>
@@ -16337,7 +15424,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>29</v>
       </c>
       <c r="C178">
         <v>1154</v>
@@ -16420,7 +15507,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>29</v>
       </c>
       <c r="C179">
         <v>1166</v>
@@ -16503,7 +15590,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>29</v>
       </c>
       <c r="C180">
         <v>1206</v>
@@ -16586,7 +15673,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>29</v>
       </c>
       <c r="C181">
         <v>1069</v>
@@ -16669,7 +15756,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>29</v>
       </c>
       <c r="C182">
         <v>1078</v>
@@ -16752,7 +15839,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>29</v>
       </c>
       <c r="C183">
         <v>1013</v>
@@ -16835,7 +15922,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="C184">
         <v>1090</v>
@@ -16918,7 +16005,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>29</v>
       </c>
       <c r="C185">
         <v>880</v>
@@ -17001,7 +16088,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>29</v>
       </c>
       <c r="C186">
         <v>1074</v>
@@ -17084,7 +16171,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>29</v>
       </c>
       <c r="C187">
         <v>1015</v>
@@ -17167,7 +16254,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>29</v>
       </c>
       <c r="C188">
         <v>938</v>
@@ -17250,7 +16337,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="C189">
         <v>936</v>
@@ -17333,7 +16420,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>29</v>
       </c>
       <c r="C190">
         <v>952</v>
@@ -17416,7 +16503,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="C191">
         <v>896</v>
@@ -17499,7 +16586,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>29</v>
       </c>
       <c r="C192">
         <v>1053</v>
@@ -17582,7 +16669,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="C193">
         <v>1088</v>
@@ -17665,7 +16752,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="C194">
         <v>1081</v>
@@ -17748,7 +16835,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>29</v>
       </c>
       <c r="C195">
         <v>992</v>
@@ -17831,7 +16918,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>29</v>
       </c>
       <c r="C196">
         <v>1158</v>
@@ -17914,7 +17001,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>29</v>
       </c>
       <c r="C197">
         <v>1138</v>
@@ -17997,7 +17084,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>29</v>
       </c>
       <c r="C198">
         <v>1119</v>
@@ -18080,7 +17167,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>29</v>
       </c>
       <c r="C199">
         <v>865</v>
@@ -18163,7 +17250,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="C200">
         <v>946</v>
@@ -18246,7 +17333,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>29</v>
       </c>
       <c r="C201">
         <v>936</v>
@@ -18329,7 +17416,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>29</v>
       </c>
       <c r="C202">
         <v>1100</v>
@@ -18412,7 +17499,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>29</v>
       </c>
       <c r="C203">
         <v>1100</v>
@@ -18495,7 +17582,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>29</v>
       </c>
       <c r="C204">
         <v>1188</v>
@@ -18578,7 +17665,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>29</v>
       </c>
       <c r="C205">
         <v>1049</v>
@@ -18661,7 +17748,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>29</v>
       </c>
       <c r="C206">
         <v>1039</v>
@@ -18744,7 +17831,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>29</v>
       </c>
       <c r="C207">
         <v>1143</v>
@@ -18827,7 +17914,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="C208">
         <v>1069</v>
@@ -18910,7 +17997,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>29</v>
       </c>
       <c r="C209">
         <v>1064</v>
@@ -18993,7 +18080,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>29</v>
       </c>
       <c r="C210">
         <v>1156</v>
@@ -19076,7 +18163,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>29</v>
       </c>
       <c r="C211">
         <v>1138</v>
@@ -19159,7 +18246,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>29</v>
       </c>
       <c r="C212">
         <v>1130</v>
@@ -19242,7 +18329,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>29</v>
       </c>
       <c r="C213">
         <v>1159</v>
@@ -19325,7 +18412,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>29</v>
       </c>
       <c r="C214">
         <v>1145</v>
@@ -19408,7 +18495,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>29</v>
       </c>
       <c r="C215">
         <v>1163</v>
@@ -19491,7 +18578,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>29</v>
       </c>
       <c r="C216">
         <v>1094</v>
@@ -19574,7 +18661,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>29</v>
       </c>
       <c r="C217">
         <v>894</v>
@@ -19657,7 +18744,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>29</v>
       </c>
       <c r="C218">
         <v>1030</v>
@@ -19740,7 +18827,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>29</v>
       </c>
       <c r="C219">
         <v>1150</v>
@@ -19823,7 +18910,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c r="C220">
         <v>1047</v>
@@ -19906,7 +18993,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>29</v>
       </c>
       <c r="C221">
         <v>769</v>
@@ -19989,7 +19076,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>29</v>
       </c>
       <c r="C222">
         <v>1106</v>
@@ -20072,7 +19159,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>29</v>
       </c>
       <c r="C223">
         <v>1153</v>
@@ -20155,7 +19242,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>29</v>
       </c>
       <c r="C224">
         <v>1108</v>
@@ -20238,7 +19325,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>29</v>
       </c>
       <c r="C225">
         <v>1200</v>
@@ -20321,7 +19408,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>29</v>
       </c>
       <c r="C226">
         <v>1159</v>
@@ -20404,7 +19491,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>29</v>
       </c>
       <c r="C227">
         <v>1059</v>
@@ -20487,7 +19574,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>29</v>
       </c>
       <c r="C228">
         <v>1139</v>
@@ -20570,7 +19657,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>29</v>
       </c>
       <c r="C229">
         <v>1039</v>
@@ -20653,7 +19740,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>29</v>
       </c>
       <c r="C230">
         <v>1028</v>
@@ -20736,7 +19823,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>29</v>
       </c>
       <c r="C231">
         <v>1175</v>
@@ -20819,7 +19906,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="C232">
         <v>1049</v>
@@ -20902,7 +19989,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>29</v>
       </c>
       <c r="C233">
         <v>1155</v>
@@ -20985,7 +20072,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="C234">
         <v>1056</v>
@@ -21068,7 +20155,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>29</v>
       </c>
       <c r="C235">
         <v>973</v>
@@ -21151,7 +20238,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>29</v>
       </c>
       <c r="C236">
         <v>846</v>
@@ -21234,7 +20321,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>29</v>
       </c>
       <c r="C237">
         <v>1020</v>
@@ -21317,7 +20404,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>29</v>
       </c>
       <c r="C238">
         <v>1082</v>
@@ -21400,7 +20487,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="C239">
         <v>1163</v>
@@ -21483,7 +20570,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="C240">
         <v>1145</v>
@@ -21566,7 +20653,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>29</v>
       </c>
       <c r="C241">
         <v>1116</v>
@@ -21649,7 +20736,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="C242">
         <v>1147</v>
@@ -21732,7 +20819,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c r="C243">
         <v>1096</v>
@@ -21815,7 +20902,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>29</v>
       </c>
       <c r="C244">
         <v>1183</v>
@@ -21898,7 +20985,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>29</v>
       </c>
       <c r="C245">
         <v>1169</v>
@@ -21981,7 +21068,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>29</v>
       </c>
       <c r="C246">
         <v>1133</v>
@@ -22064,7 +21151,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>29</v>
       </c>
       <c r="C247">
         <v>1168</v>
@@ -22147,7 +21234,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>29</v>
       </c>
       <c r="C248">
         <v>1128</v>
@@ -22230,7 +21317,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>29</v>
       </c>
       <c r="C249">
         <v>1144</v>
@@ -22313,7 +21400,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>29</v>
       </c>
       <c r="C250">
         <v>1155</v>
@@ -22396,7 +21483,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>29</v>
       </c>
       <c r="C251">
         <v>1129</v>
@@ -22479,7 +21566,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>29</v>
       </c>
       <c r="C252">
         <v>972</v>
@@ -22562,7 +21649,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
       <c r="C253">
         <v>1025</v>
@@ -22645,7 +21732,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>29</v>
       </c>
       <c r="C254">
         <v>880</v>
@@ -22728,7 +21815,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>29</v>
       </c>
       <c r="C255">
         <v>827</v>
@@ -22811,7 +21898,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>29</v>
       </c>
       <c r="C256">
         <v>1134</v>
@@ -22894,7 +21981,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>29</v>
       </c>
       <c r="C257">
         <v>1001</v>
@@ -22977,7 +22064,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>29</v>
       </c>
       <c r="C258">
         <v>1019</v>
@@ -23060,7 +22147,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>29</v>
       </c>
       <c r="C259">
         <v>1011</v>
@@ -23143,7 +22230,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>29</v>
       </c>
       <c r="C260">
         <v>1024</v>
@@ -23226,7 +22313,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="C261">
         <v>1060</v>
@@ -23309,7 +22396,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>29</v>
       </c>
       <c r="C262">
         <v>1035</v>
@@ -23392,7 +22479,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>29</v>
       </c>
       <c r="C263">
         <v>1092</v>
@@ -23475,7 +22562,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>29</v>
       </c>
       <c r="C264">
         <v>1089</v>
@@ -23558,7 +22645,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>29</v>
       </c>
       <c r="C265">
         <v>1081</v>
@@ -23641,7 +22728,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>29</v>
       </c>
       <c r="C266">
         <v>995</v>
@@ -23724,7 +22811,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>29</v>
       </c>
       <c r="C267">
         <v>929</v>
@@ -23807,7 +22894,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>29</v>
       </c>
       <c r="C268">
         <v>925</v>
@@ -23890,7 +22977,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>29</v>
       </c>
       <c r="C269">
         <v>1119</v>
@@ -23973,7 +23060,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>29</v>
       </c>
       <c r="C270">
         <v>1136</v>
@@ -24056,7 +23143,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c r="C271">
         <v>1132</v>
@@ -24139,7 +23226,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>29</v>
       </c>
       <c r="C272">
         <v>1083</v>
@@ -24222,7 +23309,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>29</v>
       </c>
       <c r="C273">
         <v>890</v>
@@ -24305,7 +23392,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>29</v>
       </c>
       <c r="C274">
         <v>1130</v>
@@ -24388,7 +23475,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>29</v>
       </c>
       <c r="C275">
         <v>1008</v>
@@ -24471,7 +23558,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>29</v>
       </c>
       <c r="C276">
         <v>1076</v>
@@ -24554,7 +23641,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>29</v>
       </c>
       <c r="C277">
         <v>1028</v>
@@ -24637,7 +23724,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>29</v>
       </c>
       <c r="C278">
         <v>1089</v>
@@ -24720,7 +23807,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>29</v>
       </c>
       <c r="C279">
         <v>944</v>
@@ -24803,7 +23890,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>29</v>
       </c>
       <c r="C280">
         <v>1197</v>
@@ -24886,7 +23973,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>29</v>
       </c>
       <c r="C281">
         <v>912</v>
@@ -24969,7 +24056,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>29</v>
       </c>
       <c r="C282">
         <v>1198</v>
@@ -25052,7 +24139,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>29</v>
       </c>
       <c r="C283">
         <v>1151</v>
@@ -25135,7 +24222,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>29</v>
       </c>
       <c r="C284">
         <v>1211</v>
@@ -25218,7 +24305,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>29</v>
       </c>
       <c r="C285">
         <v>1206</v>
@@ -25301,7 +24388,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>29</v>
       </c>
       <c r="C286">
         <v>1178</v>
@@ -25384,7 +24471,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>29</v>
       </c>
       <c r="C287">
         <v>1125</v>
@@ -25467,7 +24554,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>29</v>
       </c>
       <c r="C288">
         <v>1082</v>
@@ -25550,7 +24637,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>29</v>
       </c>
       <c r="C289">
         <v>626</v>
@@ -25633,7 +24720,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>29</v>
       </c>
       <c r="C290">
         <v>1238</v>
@@ -25716,7 +24803,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>29</v>
       </c>
       <c r="C291">
         <v>1234</v>
@@ -25799,7 +24886,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>29</v>
       </c>
       <c r="C292">
         <v>1187</v>
@@ -25882,7 +24969,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>29</v>
       </c>
       <c r="C293">
         <v>1187</v>
@@ -25965,7 +25052,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>29</v>
       </c>
       <c r="C294">
         <v>1236</v>
@@ -26048,7 +25135,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>29</v>
       </c>
       <c r="C295">
         <v>1046</v>
@@ -26131,7 +25218,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>29</v>
       </c>
       <c r="C296">
         <v>1172</v>
@@ -26214,7 +25301,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>29</v>
       </c>
       <c r="C297">
         <v>1142</v>
@@ -26297,7 +25384,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>29</v>
       </c>
       <c r="C298">
         <v>931</v>
@@ -26380,7 +25467,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>29</v>
       </c>
       <c r="C299">
         <v>877</v>
@@ -26463,7 +25550,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>29</v>
       </c>
       <c r="C300">
         <v>1076</v>
@@ -26546,7 +25633,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>29</v>
       </c>
       <c r="C301">
         <v>995</v>
@@ -26629,7 +25716,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>29</v>
       </c>
       <c r="C302">
         <v>1039</v>
@@ -26712,7 +25799,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>29</v>
       </c>
       <c r="C303">
         <v>1023</v>
@@ -26795,7 +25882,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>29</v>
       </c>
       <c r="C304">
         <v>873</v>
@@ -26878,7 +25965,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>29</v>
       </c>
       <c r="C305">
         <v>1099</v>
@@ -26961,7 +26048,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>29</v>
       </c>
       <c r="C306">
         <v>1076</v>
@@ -27044,7 +26131,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>29</v>
       </c>
       <c r="C307">
         <v>844</v>
@@ -27127,7 +26214,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>29</v>
       </c>
       <c r="C308">
         <v>909</v>
@@ -27210,7 +26297,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>29</v>
       </c>
       <c r="C309">
         <v>969</v>
@@ -27293,7 +26380,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>29</v>
       </c>
       <c r="C310">
         <v>956</v>
@@ -27376,7 +26463,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>29</v>
       </c>
       <c r="C311">
         <v>1129</v>
@@ -27459,7 +26546,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>29</v>
       </c>
       <c r="C312">
         <v>1038</v>
@@ -27542,7 +26629,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>29</v>
       </c>
       <c r="C313">
         <v>714</v>
@@ -27625,7 +26712,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>29</v>
       </c>
       <c r="C314">
         <v>780</v>
@@ -27708,7 +26795,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>29</v>
       </c>
       <c r="C315">
         <v>1203</v>
@@ -27791,7 +26878,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>29</v>
       </c>
       <c r="C316">
         <v>1086</v>
@@ -27874,7 +26961,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>29</v>
       </c>
       <c r="C317">
         <v>816</v>
@@ -27957,7 +27044,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>29</v>
       </c>
       <c r="C318">
         <v>939</v>
@@ -28040,7 +27127,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>29</v>
       </c>
       <c r="C319">
         <v>907</v>
@@ -28123,7 +27210,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>29</v>
       </c>
       <c r="C320">
         <v>1049</v>
@@ -28206,7 +27293,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>29</v>
       </c>
       <c r="C321">
         <v>1147</v>
@@ -28289,7 +27376,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>29</v>
       </c>
       <c r="C322">
         <v>1094</v>
@@ -28372,7 +27459,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>29</v>
       </c>
       <c r="C323">
         <v>1088</v>
@@ -28455,7 +27542,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>29</v>
       </c>
       <c r="C324">
         <v>1112</v>
@@ -28538,7 +27625,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>29</v>
       </c>
       <c r="C325">
         <v>850</v>
@@ -28621,7 +27708,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>29</v>
       </c>
       <c r="C326">
         <v>972</v>
@@ -28704,7 +27791,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>29</v>
       </c>
       <c r="C327">
         <v>954</v>
@@ -28787,7 +27874,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>29</v>
       </c>
       <c r="C328">
         <v>1022</v>
@@ -28870,7 +27957,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>29</v>
       </c>
       <c r="C329">
         <v>1104</v>
@@ -28953,7 +28040,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>29</v>
       </c>
       <c r="C330">
         <v>1066</v>
@@ -29036,7 +28123,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>29</v>
       </c>
       <c r="C331">
         <v>1080</v>
@@ -29119,7 +28206,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="C332">
         <v>1006</v>
@@ -29202,7 +28289,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>29</v>
       </c>
       <c r="C333">
         <v>1018</v>
@@ -29285,7 +28372,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>29</v>
       </c>
       <c r="C334">
         <v>1082</v>
@@ -29368,7 +28455,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="C335">
         <v>1099</v>
@@ -29451,7 +28538,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>29</v>
       </c>
       <c r="C336">
         <v>1135</v>
@@ -29534,7 +28621,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>29</v>
       </c>
       <c r="C337">
         <v>956</v>
@@ -29617,7 +28704,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>29</v>
       </c>
       <c r="C338">
         <v>1097</v>
@@ -29700,7 +28787,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>29</v>
       </c>
       <c r="C339">
         <v>1102</v>
@@ -29783,7 +28870,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>29</v>
       </c>
       <c r="C340">
         <v>1131</v>
@@ -29866,7 +28953,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>29</v>
       </c>
       <c r="C341">
         <v>982</v>
@@ -29949,7 +29036,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>29</v>
       </c>
       <c r="C342">
         <v>1216</v>
@@ -30032,7 +29119,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>29</v>
       </c>
       <c r="C343">
         <v>1082</v>
@@ -30115,7 +29202,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>29</v>
       </c>
       <c r="C344">
         <v>1047</v>
@@ -30198,7 +29285,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>29</v>
       </c>
       <c r="C345">
         <v>1034</v>
@@ -30281,7 +29368,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>29</v>
       </c>
       <c r="C346">
         <v>1225</v>
@@ -30364,7 +29451,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>29</v>
       </c>
       <c r="C347">
         <v>1080</v>
@@ -30447,7 +29534,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>29</v>
       </c>
       <c r="C348">
         <v>1225</v>
@@ -30530,7 +29617,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>29</v>
       </c>
       <c r="C349">
         <v>1196</v>
@@ -30613,7 +29700,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>29</v>
       </c>
       <c r="C350">
         <v>1190</v>
@@ -30696,7 +29783,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>29</v>
       </c>
       <c r="C351">
         <v>1049</v>
@@ -30779,7 +29866,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>29</v>
       </c>
       <c r="C352">
         <v>1017</v>
@@ -30862,7 +29949,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>29</v>
       </c>
       <c r="C353">
         <v>947</v>
@@ -30945,7 +30032,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>29</v>
       </c>
       <c r="C354">
         <v>1005</v>
@@ -31028,7 +30115,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>29</v>
       </c>
       <c r="C355">
         <v>1226</v>
@@ -31111,7 +30198,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>29</v>
       </c>
       <c r="C356">
         <v>1095</v>
@@ -31194,7 +30281,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>29</v>
       </c>
       <c r="C357">
         <v>1128</v>
@@ -31277,7 +30364,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>29</v>
       </c>
       <c r="C358">
         <v>1138</v>
@@ -31360,7 +30447,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>29</v>
       </c>
       <c r="C359">
         <v>1046</v>
@@ -31443,7 +30530,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>29</v>
       </c>
       <c r="C360">
         <v>803</v>
@@ -31526,7 +30613,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>29</v>
       </c>
       <c r="C361">
         <v>1008</v>
@@ -31609,7 +30696,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>29</v>
       </c>
       <c r="C362">
         <v>998</v>
@@ -31692,7 +30779,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>29</v>
       </c>
       <c r="C363">
         <v>877</v>
@@ -31775,7 +30862,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>29</v>
       </c>
       <c r="C364">
         <v>955</v>
@@ -31858,7 +30945,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>29</v>
       </c>
       <c r="C365">
         <v>841</v>
@@ -31941,7 +31028,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>29</v>
       </c>
       <c r="C366">
         <v>1112</v>
@@ -32024,7 +31111,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>29</v>
       </c>
       <c r="C367">
         <v>999</v>
@@ -32107,7 +31194,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>29</v>
       </c>
       <c r="C368">
         <v>1180</v>
@@ -32190,7 +31277,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>29</v>
       </c>
       <c r="C369">
         <v>1192</v>
@@ -32273,7 +31360,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>31</v>
       </c>
       <c r="C370">
         <v>1228</v>
@@ -32356,7 +31443,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>32</v>
       </c>
       <c r="C371">
         <v>1085</v>
@@ -32439,7 +31526,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>33</v>
       </c>
       <c r="C372">
         <v>1068</v>
@@ -32522,7 +31609,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="C373">
         <v>950</v>
@@ -32605,7 +31692,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>35</v>
       </c>
       <c r="C374">
         <v>872</v>
@@ -32688,7 +31775,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>36</v>
       </c>
       <c r="C375">
         <v>860</v>
@@ -32771,7 +31858,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>37</v>
       </c>
       <c r="C376">
         <v>1117</v>
@@ -32854,7 +31941,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>38</v>
       </c>
       <c r="C377">
         <v>1019</v>
@@ -32937,7 +32024,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>39</v>
       </c>
       <c r="C378">
         <v>1130</v>
@@ -33020,7 +32107,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>40</v>
       </c>
       <c r="C379">
         <v>1013</v>
@@ -33103,7 +32190,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>41</v>
       </c>
       <c r="C380">
         <v>983</v>
@@ -33186,7 +32273,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>42</v>
       </c>
       <c r="C381">
         <v>1046</v>
@@ -33269,7 +32356,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>43</v>
       </c>
       <c r="C382">
         <v>908</v>
@@ -33352,7 +32439,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>44</v>
       </c>
       <c r="C383">
         <v>1047</v>
@@ -33435,7 +32522,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>45</v>
       </c>
       <c r="C384">
         <v>850</v>
@@ -33518,7 +32605,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>46</v>
       </c>
       <c r="C385">
         <v>913</v>
@@ -33601,7 +32688,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>47</v>
       </c>
       <c r="C386">
         <v>852</v>
@@ -33684,7 +32771,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>48</v>
       </c>
       <c r="C387">
         <v>1127</v>
@@ -33767,7 +32854,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>49</v>
       </c>
       <c r="C388">
         <v>1091</v>
@@ -33850,7 +32937,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>50</v>
       </c>
       <c r="C389">
         <v>1065</v>
@@ -33933,7 +33020,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>51</v>
       </c>
       <c r="C390">
         <v>1048</v>
@@ -34016,7 +33103,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>52</v>
       </c>
       <c r="C391">
         <v>1091</v>
@@ -34099,7 +33186,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>53</v>
       </c>
       <c r="C392">
         <v>967</v>
@@ -34182,7 +33269,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>54</v>
       </c>
       <c r="C393">
         <v>1004</v>
@@ -34265,7 +33352,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>55</v>
       </c>
       <c r="C394">
         <v>965</v>
@@ -34348,7 +33435,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>56</v>
       </c>
       <c r="C395">
         <v>1127</v>
@@ -34431,7 +33518,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>396</v>
+        <v>57</v>
       </c>
       <c r="C396">
         <v>1125</v>
@@ -34514,7 +33601,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>397</v>
+        <v>58</v>
       </c>
       <c r="C397">
         <v>1132</v>
@@ -34597,7 +33684,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>398</v>
+        <v>59</v>
       </c>
       <c r="C398">
         <v>1069</v>
@@ -34680,7 +33767,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>60</v>
       </c>
       <c r="C399">
         <v>1100</v>
@@ -34763,7 +33850,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>400</v>
+        <v>61</v>
       </c>
       <c r="C400">
         <v>1087</v>
@@ -34846,7 +33933,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>401</v>
+        <v>62</v>
       </c>
       <c r="C401">
         <v>975</v>
@@ -34929,7 +34016,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>402</v>
+        <v>63</v>
       </c>
       <c r="C402">
         <v>1112</v>
@@ -35012,7 +34099,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>403</v>
+        <v>64</v>
       </c>
       <c r="C403">
         <v>1091</v>
@@ -35095,7 +34182,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>404</v>
+        <v>65</v>
       </c>
       <c r="C404">
         <v>1134</v>
@@ -35178,7 +34265,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>405</v>
+        <v>66</v>
       </c>
       <c r="C405">
         <v>1189</v>
@@ -35261,7 +34348,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>406</v>
+        <v>67</v>
       </c>
       <c r="C406">
         <v>1193</v>
@@ -35344,7 +34431,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>407</v>
+        <v>68</v>
       </c>
       <c r="C407">
         <v>1141</v>
@@ -35427,7 +34514,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>408</v>
+        <v>69</v>
       </c>
       <c r="C408">
         <v>1199</v>
@@ -35510,7 +34597,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>409</v>
+        <v>70</v>
       </c>
       <c r="C409">
         <v>1001</v>
@@ -35593,7 +34680,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>410</v>
+        <v>71</v>
       </c>
       <c r="C410">
         <v>1114</v>
@@ -35676,7 +34763,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>411</v>
+        <v>72</v>
       </c>
       <c r="C411">
         <v>1068</v>
@@ -35759,7 +34846,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>412</v>
+        <v>73</v>
       </c>
       <c r="C412">
         <v>1056</v>
@@ -35842,7 +34929,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>413</v>
+        <v>74</v>
       </c>
       <c r="C413">
         <v>1047</v>
@@ -35925,7 +35012,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>414</v>
+        <v>75</v>
       </c>
       <c r="C414">
         <v>1072</v>
@@ -36008,7 +35095,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>415</v>
+        <v>76</v>
       </c>
       <c r="C415">
         <v>1046</v>
@@ -36091,7 +35178,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>416</v>
+        <v>77</v>
       </c>
       <c r="C416">
         <v>970</v>
@@ -36174,7 +35261,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="C417">
         <v>996</v>
@@ -36257,7 +35344,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>418</v>
+        <v>79</v>
       </c>
       <c r="C418">
         <v>1042</v>
@@ -36340,7 +35427,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>419</v>
+        <v>80</v>
       </c>
       <c r="C419">
         <v>1081</v>
@@ -36423,7 +35510,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>420</v>
+        <v>81</v>
       </c>
       <c r="C420">
         <v>1125</v>
@@ -36506,7 +35593,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="C421">
         <v>985</v>
@@ -36589,7 +35676,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>422</v>
+        <v>83</v>
       </c>
       <c r="C422">
         <v>977</v>
@@ -36672,7 +35759,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="C423">
         <v>1031</v>
@@ -36755,7 +35842,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>424</v>
+        <v>85</v>
       </c>
       <c r="C424">
         <v>1180</v>
@@ -36838,7 +35925,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>425</v>
+        <v>86</v>
       </c>
       <c r="C425">
         <v>1173</v>
@@ -36921,7 +36008,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>87</v>
       </c>
       <c r="C426">
         <v>971</v>
@@ -37004,7 +36091,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>427</v>
+        <v>88</v>
       </c>
       <c r="C427">
         <v>1128</v>
@@ -37087,7 +36174,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>428</v>
+        <v>89</v>
       </c>
       <c r="C428">
         <v>947</v>
@@ -37170,7 +36257,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>429</v>
+        <v>90</v>
       </c>
       <c r="C429">
         <v>950</v>
@@ -37253,7 +36340,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>430</v>
+        <v>91</v>
       </c>
       <c r="C430">
         <v>991</v>
@@ -37336,7 +36423,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>431</v>
+        <v>92</v>
       </c>
       <c r="C431">
         <v>896</v>
